--- a/branches/release-candidate/ValueSet-be-vs-dispenser-types.xlsx
+++ b/branches/release-candidate/ValueSet-be-vs-dispenser-types.xlsx
@@ -60,22 +60,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-10T10:16:02+00:00</t>
+    <t>2026-03-27T06:32:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform</t>
+    <t>HL7 Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform (https://www.ehealth.fgov.be/standards/fhir, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
